--- a/PawLog_DB구조.xlsx
+++ b/PawLog_DB구조.xlsx
@@ -12,6 +12,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📷 sns_posts" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="💬 sns_comments" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🗺️ ERD 다이어그램" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="👥 sns_follows" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📖 sns_stories" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="👁 sns_story_views" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="❤ sns_likes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🖼 sns_post_images" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏷 sns_hashtags" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🔗 sns_post_hashtags" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🐾 sns_pets" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🔑 sns_social_accounts" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🚨 sns_comment_reports" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🐶 sns_post_pet_tags" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⚠ 기존테이블 보완사항" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 추가DB 개요(Ver2.0)" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +34,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -162,8 +175,71 @@
       <color rgb="002E7D32"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="00333333"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <i val="1"/>
+      <color rgb="00333333"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00856404"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <color rgb="00721C24"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -215,8 +291,23 @@
         <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9534F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -296,11 +387,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00FF8C42"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00FF8C42"/>
+      </right>
+      <top style="medium">
+        <color rgb="00FF8C42"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00FF8C42"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00FF8C42"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00FF8C42"/>
+      </right>
+      <top style="medium">
+        <color rgb="00FF8C42"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00FF8C42"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -546,6 +695,56 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -929,6 +1128,14 @@
           <t>🐾  PawLog SNS — 데이터베이스 구조 정리</t>
         </is>
       </c>
+      <c r="B2" s="84" t="n"/>
+      <c r="C2" s="84" t="n"/>
+      <c r="D2" s="84" t="n"/>
+      <c r="E2" s="84" t="n"/>
+      <c r="F2" s="84" t="n"/>
+      <c r="G2" s="84" t="n"/>
+      <c r="H2" s="84" t="n"/>
+      <c r="I2" s="85" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -936,6 +1143,14 @@
           <t>테이블 prefix: sns_   |   작성일: 2026-02-26   |   Ver 1.0</t>
         </is>
       </c>
+      <c r="B3" s="84" t="n"/>
+      <c r="C3" s="84" t="n"/>
+      <c r="D3" s="84" t="n"/>
+      <c r="E3" s="84" t="n"/>
+      <c r="F3" s="84" t="n"/>
+      <c r="G3" s="84" t="n"/>
+      <c r="H3" s="84" t="n"/>
+      <c r="I3" s="85" t="n"/>
     </row>
     <row r="4" ht="14" customHeight="1"/>
     <row r="5" ht="16" customHeight="1">
@@ -944,6 +1159,14 @@
           <t>⚠️  충돌 방지 주의사항</t>
         </is>
       </c>
+      <c r="B5" s="84" t="n"/>
+      <c r="C5" s="84" t="n"/>
+      <c r="D5" s="84" t="n"/>
+      <c r="E5" s="84" t="n"/>
+      <c r="F5" s="84" t="n"/>
+      <c r="G5" s="84" t="n"/>
+      <c r="H5" s="84" t="n"/>
+      <c r="I5" s="85" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -951,6 +1174,14 @@
           <t>기존 테이블과의 충돌 방지를 위해 모든 테이블명에 'sns_' prefix를 적용합니다.</t>
         </is>
       </c>
+      <c r="B6" s="84" t="n"/>
+      <c r="C6" s="84" t="n"/>
+      <c r="D6" s="84" t="n"/>
+      <c r="E6" s="84" t="n"/>
+      <c r="F6" s="84" t="n"/>
+      <c r="G6" s="84" t="n"/>
+      <c r="H6" s="84" t="n"/>
+      <c r="I6" s="85" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -958,6 +1189,14 @@
           <t>예시: users → sns_users  /  posts → sns_posts  /  comments → sns_comments</t>
         </is>
       </c>
+      <c r="B7" s="84" t="n"/>
+      <c r="C7" s="84" t="n"/>
+      <c r="D7" s="84" t="n"/>
+      <c r="E7" s="84" t="n"/>
+      <c r="F7" s="84" t="n"/>
+      <c r="G7" s="84" t="n"/>
+      <c r="H7" s="84" t="n"/>
+      <c r="I7" s="85" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -965,6 +1204,14 @@
           <t>충돌이 의심될 경우 SHOW TABLES LIKE 'sns_%'; 명령으로 기존 테이블 여부를 먼저 확인하세요.</t>
         </is>
       </c>
+      <c r="B8" s="84" t="n"/>
+      <c r="C8" s="84" t="n"/>
+      <c r="D8" s="84" t="n"/>
+      <c r="E8" s="84" t="n"/>
+      <c r="F8" s="84" t="n"/>
+      <c r="G8" s="84" t="n"/>
+      <c r="H8" s="84" t="n"/>
+      <c r="I8" s="85" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1"/>
     <row r="10" ht="14" customHeight="1"/>
@@ -974,6 +1221,14 @@
           <t>📦  테이블 목록 요약</t>
         </is>
       </c>
+      <c r="B11" s="84" t="n"/>
+      <c r="C11" s="84" t="n"/>
+      <c r="D11" s="84" t="n"/>
+      <c r="E11" s="84" t="n"/>
+      <c r="F11" s="84" t="n"/>
+      <c r="G11" s="84" t="n"/>
+      <c r="H11" s="84" t="n"/>
+      <c r="I11" s="85" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -1090,6 +1345,14 @@
           <t>🔗  테이블 관계 요약 (ERD 간략)</t>
         </is>
       </c>
+      <c r="B18" s="84" t="n"/>
+      <c r="C18" s="84" t="n"/>
+      <c r="D18" s="84" t="n"/>
+      <c r="E18" s="84" t="n"/>
+      <c r="F18" s="84" t="n"/>
+      <c r="G18" s="84" t="n"/>
+      <c r="H18" s="84" t="n"/>
+      <c r="I18" s="85" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1206,6 +1469,14 @@
           <t>📌  설계 특이사항 및 기술 메모</t>
         </is>
       </c>
+      <c r="B25" s="84" t="n"/>
+      <c r="C25" s="84" t="n"/>
+      <c r="D25" s="84" t="n"/>
+      <c r="E25" s="84" t="n"/>
+      <c r="F25" s="84" t="n"/>
+      <c r="G25" s="84" t="n"/>
+      <c r="H25" s="84" t="n"/>
+      <c r="I25" s="85" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
@@ -1218,6 +1489,9 @@
           <t>별도 likes 테이블 없음 — sns_posts.likes_count 필드에 정수 직접 저장 (단순화 설계)</t>
         </is>
       </c>
+      <c r="C26" s="84" t="n"/>
+      <c r="D26" s="84" t="n"/>
+      <c r="E26" s="85" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
@@ -1230,6 +1504,9 @@
           <t>파일 직접 업로드 없음 — Unsplash API에서 선택한 이미지 URL 문자열로 저장</t>
         </is>
       </c>
+      <c r="C27" s="84" t="n"/>
+      <c r="D27" s="84" t="n"/>
+      <c r="E27" s="85" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
@@ -1242,6 +1519,9 @@
           <t>비밀번호는 반드시 bcrypt 등 해시 알고리즘으로 암호화 후 저장 (평문 저장 금지)</t>
         </is>
       </c>
+      <c r="C28" s="84" t="n"/>
+      <c r="D28" s="84" t="n"/>
+      <c r="E28" s="85" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
@@ -1254,6 +1534,9 @@
           <t>현재 설계는 하드 삭제 기준 — 추후 is_deleted, deleted_at 컬럼 추가 고려</t>
         </is>
       </c>
+      <c r="C29" s="84" t="n"/>
+      <c r="D29" s="84" t="n"/>
+      <c r="E29" s="85" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
@@ -1266,13 +1549,16 @@
           <t>user_id, post_id, created_at 컬럼에 INDEX 추가 권장 (피드 조회 성능)</t>
         </is>
       </c>
+      <c r="C30" s="84" t="n"/>
+      <c r="D30" s="84" t="n"/>
+      <c r="E30" s="85" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A25:I25"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
+    <mergeCell ref="A25:I25"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A11:I11"/>
     <mergeCell ref="A5:I5"/>
@@ -1283,6 +1569,4273 @@
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="B28:E28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="86" t="inlineStr">
+        <is>
+          <t>🖼  테이블: sns_post_images   —   게시물 다중 이미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>게시물 1개에 이미지 최대 10장 저장 | 기획서: 이미지 슬라이더 최대 10장</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="88" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="88" t="inlineStr">
+        <is>
+          <t>컬럼명 (Column)</t>
+        </is>
+      </c>
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>데이터 타입</t>
+        </is>
+      </c>
+      <c r="D3" s="88" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="E3" s="88" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="F3" s="88" t="inlineStr">
+        <is>
+          <t>키 유형</t>
+        </is>
+      </c>
+      <c r="G3" s="88" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="H3" s="88" t="inlineStr">
+        <is>
+          <t>사용 화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="89" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B4" s="89" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D4" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E4" s="90" t="inlineStr">
+        <is>
+          <t>AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="F4" s="89" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G4" s="90" t="inlineStr">
+        <is>
+          <t>이미지 고유 번호</t>
+        </is>
+      </c>
+      <c r="H4" s="90" t="inlineStr">
+        <is>
+          <t>게시물 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B5" s="91" t="inlineStr">
+        <is>
+          <t>post_id</t>
+        </is>
+      </c>
+      <c r="C5" s="92" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D5" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E5" s="92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="91" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G5" s="92" t="inlineStr">
+        <is>
+          <t>연결된 게시물 — sns_posts.id 참조</t>
+        </is>
+      </c>
+      <c r="H5" s="92" t="inlineStr">
+        <is>
+          <t>게시물 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="89" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>image_url</t>
+        </is>
+      </c>
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>VARCHAR(500)</t>
+        </is>
+      </c>
+      <c r="D6" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E6" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="90" t="inlineStr">
+        <is>
+          <t>Unsplash API 이미지 URL</t>
+        </is>
+      </c>
+      <c r="H6" s="90" t="inlineStr">
+        <is>
+          <t>게시물 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="91" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="C7" s="92" t="inlineStr">
+        <is>
+          <t>TINYINT</t>
+        </is>
+      </c>
+      <c r="D7" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E7" s="92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="92" t="inlineStr">
+        <is>
+          <t>이미지 순서 0~9 (0=대표 이미지, 슬라이더 순서)</t>
+        </is>
+      </c>
+      <c r="H7" s="92" t="inlineStr">
+        <is>
+          <t>게시물 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="89" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B8" s="89" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C8" s="90" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D8" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E8" s="90" t="inlineStr">
+        <is>
+          <t>NOW()</t>
+        </is>
+      </c>
+      <c r="F8" s="89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="90" t="inlineStr">
+        <is>
+          <t>이미지 등록 일시</t>
+        </is>
+      </c>
+      <c r="H8" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="96" t="inlineStr">
+        <is>
+          <t>📌 설계 주의사항: sns_posts.image_url은 대표 썸네일(sort_order=0)로 유지. 다중 이미지는 이 테이블로 관리</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="93" t="inlineStr">
+        <is>
+          <t>🛠️  CREATE TABLE SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="94" t="inlineStr">
+        <is>
+          <t>CREATE TABLE sns_post_images (</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    id         INT           NOT NULL AUTO_INCREMENT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    post_id    INT           NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    image_url  VARCHAR(500)  NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    sort_order TINYINT       NOT NULL DEFAULT 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    created_at DATETIME      NOT NULL DEFAULT NOW(),</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PRIMARY KEY (id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_post_id (post_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (post_id) REFERENCES sns_posts(id) ON DELETE CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="94" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="86" t="inlineStr">
+        <is>
+          <t>🏷  테이블: sns_hashtags   —   해시태그 마스터</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>해시태그 중복 없이 저장하는 마스터 테이블 | 기획서: 해시태그 자동 감지 + 탐색/검색</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="88" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="88" t="inlineStr">
+        <is>
+          <t>컬럼명 (Column)</t>
+        </is>
+      </c>
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>데이터 타입</t>
+        </is>
+      </c>
+      <c r="D3" s="88" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="E3" s="88" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="F3" s="88" t="inlineStr">
+        <is>
+          <t>키 유형</t>
+        </is>
+      </c>
+      <c r="G3" s="88" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="H3" s="88" t="inlineStr">
+        <is>
+          <t>사용 화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="89" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B4" s="89" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D4" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E4" s="90" t="inlineStr">
+        <is>
+          <t>AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="F4" s="89" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G4" s="90" t="inlineStr">
+        <is>
+          <t>해시태그 고유 번호</t>
+        </is>
+      </c>
+      <c r="H4" s="90" t="inlineStr">
+        <is>
+          <t>탐색/검색</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B5" s="91" t="inlineStr">
+        <is>
+          <t>tag_name</t>
+        </is>
+      </c>
+      <c r="C5" s="92" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="D5" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E5" s="92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="91" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
+      <c r="G5" s="92" t="inlineStr">
+        <is>
+          <t>해시태그 텍스트 (# 제외, 소문자 정규화)</t>
+        </is>
+      </c>
+      <c r="H5" s="92" t="inlineStr">
+        <is>
+          <t>탐색/검색</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="89" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>use_count</t>
+        </is>
+      </c>
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D6" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E6" s="90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="90" t="inlineStr">
+        <is>
+          <t>사용 횟수 캐시 (인기 태그 정렬, 자동완성용)</t>
+        </is>
+      </c>
+      <c r="H6" s="90" t="inlineStr">
+        <is>
+          <t>탐색/검색</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="91" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C7" s="92" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D7" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E7" s="92" t="inlineStr">
+        <is>
+          <t>NOW()</t>
+        </is>
+      </c>
+      <c r="F7" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="92" t="inlineStr">
+        <is>
+          <t>최초 사용 일시</t>
+        </is>
+      </c>
+      <c r="H7" s="92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="93" t="inlineStr">
+        <is>
+          <t>🛠️  CREATE TABLE SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="94" t="inlineStr">
+        <is>
+          <t>CREATE TABLE sns_hashtags (</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    id         INT           NOT NULL AUTO_INCREMENT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    tag_name   VARCHAR(100)  NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    use_count  INT           NOT NULL DEFAULT 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    created_at DATETIME      NOT NULL DEFAULT NOW(),</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PRIMARY KEY (id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    UNIQUE KEY uq_tag_name (tag_name),</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_use_count (use_count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="86" t="inlineStr">
+        <is>
+          <t>🔗  테이블: sns_post_hashtags   —   게시물-해시태그 연결</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>게시물 ↔ 해시태그 M:N 연결 테이블 | 기획서: 해시태그 검색 및 탐색 페이지</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="88" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="88" t="inlineStr">
+        <is>
+          <t>컬럼명 (Column)</t>
+        </is>
+      </c>
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>데이터 타입</t>
+        </is>
+      </c>
+      <c r="D3" s="88" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="E3" s="88" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="F3" s="88" t="inlineStr">
+        <is>
+          <t>키 유형</t>
+        </is>
+      </c>
+      <c r="G3" s="88" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="H3" s="88" t="inlineStr">
+        <is>
+          <t>사용 화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="89" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B4" s="89" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D4" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E4" s="90" t="inlineStr">
+        <is>
+          <t>AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="F4" s="89" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G4" s="90" t="inlineStr">
+        <is>
+          <t>연결 고유 번호</t>
+        </is>
+      </c>
+      <c r="H4" s="90" t="inlineStr">
+        <is>
+          <t>탐색/검색</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B5" s="91" t="inlineStr">
+        <is>
+          <t>post_id</t>
+        </is>
+      </c>
+      <c r="C5" s="92" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D5" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E5" s="92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="91" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G5" s="92" t="inlineStr">
+        <is>
+          <t>게시물 — sns_posts.id 참조</t>
+        </is>
+      </c>
+      <c r="H5" s="92" t="inlineStr">
+        <is>
+          <t>탐색/검색</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="89" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>hashtag_id</t>
+        </is>
+      </c>
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D6" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E6" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="89" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G6" s="90" t="inlineStr">
+        <is>
+          <t>해시태그 — sns_hashtags.id 참조</t>
+        </is>
+      </c>
+      <c r="H6" s="90" t="inlineStr">
+        <is>
+          <t>탐색/검색</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="93" t="inlineStr">
+        <is>
+          <t>🛠️  CREATE TABLE SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="94" t="inlineStr">
+        <is>
+          <t>CREATE TABLE sns_post_hashtags (</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    id         INT  NOT NULL AUTO_INCREMENT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    post_id    INT  NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    hashtag_id INT  NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PRIMARY KEY (id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    UNIQUE KEY uq_post_hashtag (post_id, hashtag_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_hashtag_id (hashtag_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_post_id    (post_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (post_id)    REFERENCES sns_posts(id)    ON DELETE CASCADE,</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (hashtag_id) REFERENCES sns_hashtags(id) ON DELETE CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="94" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="86" t="inlineStr">
+        <is>
+          <t>🐾  테이블: sns_pets   —   반려동물 프로필</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>반려동물 개별 등록 (다두 가구 지원) | 1차 필수 기능: 반려동물 프로필</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="88" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="88" t="inlineStr">
+        <is>
+          <t>컬럼명 (Column)</t>
+        </is>
+      </c>
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>데이터 타입</t>
+        </is>
+      </c>
+      <c r="D3" s="88" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="E3" s="88" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="F3" s="88" t="inlineStr">
+        <is>
+          <t>키 유형</t>
+        </is>
+      </c>
+      <c r="G3" s="88" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="H3" s="88" t="inlineStr">
+        <is>
+          <t>사용 화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="89" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B4" s="89" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D4" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E4" s="90" t="inlineStr">
+        <is>
+          <t>AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="F4" s="89" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G4" s="90" t="inlineStr">
+        <is>
+          <t>반려동물 고유 번호</t>
+        </is>
+      </c>
+      <c r="H4" s="90" t="inlineStr">
+        <is>
+          <t>마이페이지, 온보딩</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B5" s="91" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C5" s="92" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D5" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E5" s="92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="91" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G5" s="92" t="inlineStr">
+        <is>
+          <t>보호자 — sns_users.id 참조</t>
+        </is>
+      </c>
+      <c r="H5" s="92" t="inlineStr">
+        <is>
+          <t>마이페이지</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="89" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="D6" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E6" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="90" t="inlineStr">
+        <is>
+          <t>반려동물 이름</t>
+        </is>
+      </c>
+      <c r="H6" s="90" t="inlineStr">
+        <is>
+          <t>마이페이지, 피드</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="91" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="C7" s="92" t="inlineStr">
+        <is>
+          <t>ENUM</t>
+        </is>
+      </c>
+      <c r="D7" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E7" s="92" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F7" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="92" t="inlineStr">
+        <is>
+          <t>종류: '강아지' | '고양이' | '기타'</t>
+        </is>
+      </c>
+      <c r="H7" s="92" t="inlineStr">
+        <is>
+          <t>마이페이지, 탐색</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="89" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B8" s="89" t="inlineStr">
+        <is>
+          <t>breed</t>
+        </is>
+      </c>
+      <c r="C8" s="90" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="D8" s="90" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E8" s="90" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F8" s="89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="90" t="inlineStr">
+        <is>
+          <t>세부 품종 (예: 골든 리트리버, 러시안블루)</t>
+        </is>
+      </c>
+      <c r="H8" s="90" t="inlineStr">
+        <is>
+          <t>마이페이지</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="91" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B9" s="91" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="C9" s="92" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D9" s="92" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E9" s="92" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F9" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="92" t="inlineStr">
+        <is>
+          <t>반려동물 생일 (나이 자동 계산용)</t>
+        </is>
+      </c>
+      <c r="H9" s="92" t="inlineStr">
+        <is>
+          <t>마이페이지</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="89" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B10" s="89" t="inlineStr">
+        <is>
+          <t>bio</t>
+        </is>
+      </c>
+      <c r="C10" s="90" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D10" s="90" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E10" s="90" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F10" s="89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="90" t="inlineStr">
+        <is>
+          <t>반려동물 소개글</t>
+        </is>
+      </c>
+      <c r="H10" s="90" t="inlineStr">
+        <is>
+          <t>마이페이지</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="91" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B11" s="91" t="inlineStr">
+        <is>
+          <t>profile_image</t>
+        </is>
+      </c>
+      <c r="C11" s="92" t="inlineStr">
+        <is>
+          <t>VARCHAR(300)</t>
+        </is>
+      </c>
+      <c r="D11" s="92" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E11" s="92" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F11" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="92" t="inlineStr">
+        <is>
+          <t>반려동물 프로필 사진 URL</t>
+        </is>
+      </c>
+      <c r="H11" s="92" t="inlineStr">
+        <is>
+          <t>마이페이지, 피드</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="89" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B12" s="89" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C12" s="90" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D12" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E12" s="90" t="inlineStr">
+        <is>
+          <t>NOW()</t>
+        </is>
+      </c>
+      <c r="F12" s="89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="90" t="inlineStr">
+        <is>
+          <t>등록 일시</t>
+        </is>
+      </c>
+      <c r="H12" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="93" t="inlineStr">
+        <is>
+          <t>🛠️  CREATE TABLE SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t>CREATE TABLE sns_pets (</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    id            INT                             NOT NULL AUTO_INCREMENT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    user_id       INT                             NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    name          VARCHAR(50)                     NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    species       ENUM('강아지','고양이','기타')  NOT NULL DEFAULT '기타',</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    breed         VARCHAR(100)                    NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    birthday      DATE                            NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    bio           TEXT                            NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    profile_image VARCHAR(300)                    NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    created_at    DATETIME                        NOT NULL DEFAULT NOW(),</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PRIMARY KEY (id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_user_id (user_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (user_id) REFERENCES sns_users(id) ON DELETE CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="94" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="86" t="inlineStr">
+        <is>
+          <t>🔑  테이블: sns_social_accounts   —   소셜 로그인 연동</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>카카오 / 구글 OAuth 2.0 소셜 계정 정보 저장 | 1차 필수 기능: 소셜 로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="88" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="88" t="inlineStr">
+        <is>
+          <t>컬럼명 (Column)</t>
+        </is>
+      </c>
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>데이터 타입</t>
+        </is>
+      </c>
+      <c r="D3" s="88" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="E3" s="88" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="F3" s="88" t="inlineStr">
+        <is>
+          <t>키 유형</t>
+        </is>
+      </c>
+      <c r="G3" s="88" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="H3" s="88" t="inlineStr">
+        <is>
+          <t>사용 화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="89" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B4" s="89" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D4" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E4" s="90" t="inlineStr">
+        <is>
+          <t>AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="F4" s="89" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G4" s="90" t="inlineStr">
+        <is>
+          <t>소셜 계정 연결 고유 번호</t>
+        </is>
+      </c>
+      <c r="H4" s="90" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B5" s="91" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C5" s="92" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D5" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E5" s="92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="91" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G5" s="92" t="inlineStr">
+        <is>
+          <t>연결된 사용자 — sns_users.id 참조</t>
+        </is>
+      </c>
+      <c r="H5" s="92" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="89" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>provider</t>
+        </is>
+      </c>
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>ENUM</t>
+        </is>
+      </c>
+      <c r="D6" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E6" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="89" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
+      <c r="G6" s="90" t="inlineStr">
+        <is>
+          <t>소셜 플랫폼: 'kakao' | 'google'</t>
+        </is>
+      </c>
+      <c r="H6" s="90" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="91" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>provider_id</t>
+        </is>
+      </c>
+      <c r="C7" s="92" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="D7" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E7" s="92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="91" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
+      <c r="G7" s="92" t="inlineStr">
+        <is>
+          <t>소셜 플랫폼 사용자 고유 ID (OAuth sub 값)</t>
+        </is>
+      </c>
+      <c r="H7" s="92" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="89" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B8" s="89" t="inlineStr">
+        <is>
+          <t>access_token</t>
+        </is>
+      </c>
+      <c r="C8" s="90" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D8" s="90" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E8" s="90" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F8" s="89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="90" t="inlineStr">
+        <is>
+          <t>OAuth Access Token (서버 저장 여부는 선택)</t>
+        </is>
+      </c>
+      <c r="H8" s="90" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="91" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B9" s="91" t="inlineStr">
+        <is>
+          <t>refresh_token</t>
+        </is>
+      </c>
+      <c r="C9" s="92" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D9" s="92" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E9" s="92" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F9" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="92" t="inlineStr">
+        <is>
+          <t>OAuth Refresh Token (서버 저장 여부는 선택)</t>
+        </is>
+      </c>
+      <c r="H9" s="92" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="89" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B10" s="89" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C10" s="90" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D10" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E10" s="90" t="inlineStr">
+        <is>
+          <t>NOW()</t>
+        </is>
+      </c>
+      <c r="F10" s="89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="90" t="inlineStr">
+        <is>
+          <t>소셜 계정 최초 연결 일시</t>
+        </is>
+      </c>
+      <c r="H10" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="93" t="inlineStr">
+        <is>
+          <t>🛠️  CREATE TABLE SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t>CREATE TABLE sns_social_accounts (</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    id            INT                    NOT NULL AUTO_INCREMENT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    user_id       INT                    NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    provider      ENUM('kakao','google') NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    provider_id   VARCHAR(100)           NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    access_token  TEXT                   NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    refresh_token TEXT                   NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    created_at    DATETIME               NOT NULL DEFAULT NOW(),</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PRIMARY KEY (id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    UNIQUE KEY uq_provider (provider, provider_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_user_id (user_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (user_id) REFERENCES sns_users(id) ON DELETE CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="94" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="86" t="inlineStr">
+        <is>
+          <t>🚨  테이블: sns_comment_reports   —   댓글 신고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>부적절한 댓글 신고 기록 저장 | 1차 필수 기능: 좋아요 &amp; 댓글 (댓글 신고)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="88" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="88" t="inlineStr">
+        <is>
+          <t>컬럼명 (Column)</t>
+        </is>
+      </c>
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>데이터 타입</t>
+        </is>
+      </c>
+      <c r="D3" s="88" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="E3" s="88" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="F3" s="88" t="inlineStr">
+        <is>
+          <t>키 유형</t>
+        </is>
+      </c>
+      <c r="G3" s="88" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="H3" s="88" t="inlineStr">
+        <is>
+          <t>사용 화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="89" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B4" s="89" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D4" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E4" s="90" t="inlineStr">
+        <is>
+          <t>AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="F4" s="89" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G4" s="90" t="inlineStr">
+        <is>
+          <t>신고 고유 번호</t>
+        </is>
+      </c>
+      <c r="H4" s="90" t="inlineStr">
+        <is>
+          <t>게시물 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B5" s="91" t="inlineStr">
+        <is>
+          <t>comment_id</t>
+        </is>
+      </c>
+      <c r="C5" s="92" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D5" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E5" s="92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="91" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G5" s="92" t="inlineStr">
+        <is>
+          <t>신고된 댓글 — sns_comments.id 참조</t>
+        </is>
+      </c>
+      <c r="H5" s="92" t="inlineStr">
+        <is>
+          <t>게시물 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="89" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>reporter_id</t>
+        </is>
+      </c>
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D6" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E6" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="89" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G6" s="90" t="inlineStr">
+        <is>
+          <t>신고한 사용자 — sns_users.id 참조</t>
+        </is>
+      </c>
+      <c r="H6" s="90" t="inlineStr">
+        <is>
+          <t>게시물 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="91" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="C7" s="92" t="inlineStr">
+        <is>
+          <t>ENUM</t>
+        </is>
+      </c>
+      <c r="D7" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E7" s="92" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F7" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="92" t="inlineStr">
+        <is>
+          <t>신고 사유: '스팸' | '욕설/혐오' | '성인' | '기타'</t>
+        </is>
+      </c>
+      <c r="H7" s="92" t="inlineStr">
+        <is>
+          <t>게시물 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="89" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B8" s="89" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C8" s="90" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D8" s="90" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E8" s="90" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F8" s="89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="90" t="inlineStr">
+        <is>
+          <t>신고 상세 내용 (선택 입력)</t>
+        </is>
+      </c>
+      <c r="H8" s="90" t="inlineStr">
+        <is>
+          <t>게시물 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="91" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B9" s="91" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C9" s="92" t="inlineStr">
+        <is>
+          <t>ENUM</t>
+        </is>
+      </c>
+      <c r="D9" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E9" s="92" t="inlineStr">
+        <is>
+          <t>접수</t>
+        </is>
+      </c>
+      <c r="F9" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="92" t="inlineStr">
+        <is>
+          <t>처리 상태: '접수' | '검토중' | '처리완료' | '기각'</t>
+        </is>
+      </c>
+      <c r="H9" s="92" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="89" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B10" s="89" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C10" s="90" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D10" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E10" s="90" t="inlineStr">
+        <is>
+          <t>NOW()</t>
+        </is>
+      </c>
+      <c r="F10" s="89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="90" t="inlineStr">
+        <is>
+          <t>신고 일시</t>
+        </is>
+      </c>
+      <c r="H10" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="93" t="inlineStr">
+        <is>
+          <t>🛠️  CREATE TABLE SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t>CREATE TABLE sns_comment_reports (</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    id          INT                                    NOT NULL AUTO_INCREMENT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    comment_id  INT                                    NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    reporter_id INT                                    NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    reason      ENUM('스팸','욕설/혐오','성인','기타') NOT NULL DEFAULT '기타',</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    detail      TEXT                                   NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    status      ENUM('접수','검토중','처리완료','기각') NOT NULL DEFAULT '접수',</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    created_at  DATETIME                               NOT NULL DEFAULT NOW(),</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PRIMARY KEY (id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    UNIQUE KEY uq_report (comment_id, reporter_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_comment_id  (comment_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_reporter_id (reporter_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (comment_id)  REFERENCES sns_comments(id) ON DELETE CASCADE,</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (reporter_id) REFERENCES sns_users(id)    ON DELETE CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="94" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="86" t="inlineStr">
+        <is>
+          <t>🐶  테이블: sns_post_pet_tags   —   게시물 반려동물 태그</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>게시물에 반려동물 태그 연결 M:N | 기획서: 게시물 작성 — 반려동물 태그</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="88" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="88" t="inlineStr">
+        <is>
+          <t>컬럼명 (Column)</t>
+        </is>
+      </c>
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>데이터 타입</t>
+        </is>
+      </c>
+      <c r="D3" s="88" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="E3" s="88" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="F3" s="88" t="inlineStr">
+        <is>
+          <t>키 유형</t>
+        </is>
+      </c>
+      <c r="G3" s="88" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="H3" s="88" t="inlineStr">
+        <is>
+          <t>사용 화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="89" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B4" s="89" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D4" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E4" s="90" t="inlineStr">
+        <is>
+          <t>AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="F4" s="89" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G4" s="90" t="inlineStr">
+        <is>
+          <t>태그 연결 고유 번호</t>
+        </is>
+      </c>
+      <c r="H4" s="90" t="inlineStr">
+        <is>
+          <t>게시물 작성, 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B5" s="91" t="inlineStr">
+        <is>
+          <t>post_id</t>
+        </is>
+      </c>
+      <c r="C5" s="92" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D5" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E5" s="92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="91" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G5" s="92" t="inlineStr">
+        <is>
+          <t>게시물 — sns_posts.id 참조</t>
+        </is>
+      </c>
+      <c r="H5" s="92" t="inlineStr">
+        <is>
+          <t>게시물 작성, 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="89" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>pet_id</t>
+        </is>
+      </c>
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D6" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E6" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="89" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G6" s="90" t="inlineStr">
+        <is>
+          <t>태그된 반려동물 — sns_pets.id 참조</t>
+        </is>
+      </c>
+      <c r="H6" s="90" t="inlineStr">
+        <is>
+          <t>게시물 작성, 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="93" t="inlineStr">
+        <is>
+          <t>🛠️  CREATE TABLE SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="94" t="inlineStr">
+        <is>
+          <t>CREATE TABLE sns_post_pet_tags (</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    id      INT  NOT NULL AUTO_INCREMENT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    post_id INT  NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    pet_id  INT  NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PRIMARY KEY (id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    UNIQUE KEY uq_post_pet (post_id, pet_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_post_id (post_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_pet_id  (pet_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (post_id) REFERENCES sns_posts(id) ON DELETE CASCADE,</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (pet_id)  REFERENCES sns_pets(id)  ON DELETE CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="94" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="97" t="inlineStr">
+        <is>
+          <t>⚠️  기존 테이블 보완 권고사항 (ALTER TABLE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="98" t="inlineStr">
+        <is>
+          <t>기존 3개 테이블(sns_users / sns_posts / sns_comments)을 수정하지 않고, 아래 ALTER TABLE 구문을 추가 실행하면 필수 기능 완성 가능합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="99" t="inlineStr">
+        <is>
+          <t>대상 테이블</t>
+        </is>
+      </c>
+      <c r="B4" s="99" t="inlineStr">
+        <is>
+          <t>추가 컬럼명</t>
+        </is>
+      </c>
+      <c r="C4" s="99" t="inlineStr">
+        <is>
+          <t>데이터 타입</t>
+        </is>
+      </c>
+      <c r="D4" s="99" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E4" s="99" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="F4" s="99" t="inlineStr">
+        <is>
+          <t>우선순위</t>
+        </is>
+      </c>
+      <c r="G4" s="99" t="inlineStr">
+        <is>
+          <t>추가 이유 (기획서 근거)</t>
+        </is>
+      </c>
+      <c r="H4" s="99" t="inlineStr">
+        <is>
+          <t>관련 기능</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="89" t="inlineStr">
+        <is>
+          <t>sns_comments</t>
+        </is>
+      </c>
+      <c r="B5" s="89" t="inlineStr">
+        <is>
+          <t>parent_comment_id</t>
+        </is>
+      </c>
+      <c r="C5" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D5" s="90" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E5" s="90" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F5" s="90" t="inlineStr">
+        <is>
+          <t>🔴 필수</t>
+        </is>
+      </c>
+      <c r="G5" s="90" t="inlineStr">
+        <is>
+          <t>대댓글 기능 — 기획서: 댓글/대댓글 스레드. NULL=최상위 댓글, 값 있으면 대댓글</t>
+        </is>
+      </c>
+      <c r="H5" s="90" t="inlineStr">
+        <is>
+          <t>댓글/대댓글</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="91" t="inlineStr">
+        <is>
+          <t>sns_posts</t>
+        </is>
+      </c>
+      <c r="B6" s="91" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C6" s="92" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D6" s="92" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E6" s="92" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F6" s="92" t="inlineStr">
+        <is>
+          <t>🔴 필수</t>
+        </is>
+      </c>
+      <c r="G6" s="92" t="inlineStr">
+        <is>
+          <t>게시물 수정 일시 추적 — 기획서: 게시물 CRUD (수정 기능)</t>
+        </is>
+      </c>
+      <c r="H6" s="92" t="inlineStr">
+        <is>
+          <t>게시물 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="89" t="inlineStr">
+        <is>
+          <t>sns_users</t>
+        </is>
+      </c>
+      <c r="B7" s="89" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C7" s="90" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D7" s="90" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E7" s="90" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F7" s="90" t="inlineStr">
+        <is>
+          <t>🟡 권장</t>
+        </is>
+      </c>
+      <c r="G7" s="90" t="inlineStr">
+        <is>
+          <t>프로필 최종 수정일 추적 — 마이페이지 프로필 편집 기능 대응</t>
+        </is>
+      </c>
+      <c r="H7" s="90" t="inlineStr">
+        <is>
+          <t>마이페이지</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="91" t="inlineStr">
+        <is>
+          <t>sns_posts</t>
+        </is>
+      </c>
+      <c r="B8" s="91" t="inlineStr">
+        <is>
+          <t>is_deleted</t>
+        </is>
+      </c>
+      <c r="C8" s="92" t="inlineStr">
+        <is>
+          <t>TINYINT(1)</t>
+        </is>
+      </c>
+      <c r="D8" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E8" s="92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="92" t="inlineStr">
+        <is>
+          <t>🟡 권장</t>
+        </is>
+      </c>
+      <c r="G8" s="92" t="inlineStr">
+        <is>
+          <t>소프트 삭제 지원 — DB 개요 설계 메모에서 언급. 삭제 후 복구 가능</t>
+        </is>
+      </c>
+      <c r="H8" s="92" t="inlineStr">
+        <is>
+          <t>게시물 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="89" t="inlineStr">
+        <is>
+          <t>sns_users</t>
+        </is>
+      </c>
+      <c r="B9" s="89" t="inlineStr">
+        <is>
+          <t>is_active</t>
+        </is>
+      </c>
+      <c r="C9" s="90" t="inlineStr">
+        <is>
+          <t>TINYINT(1)</t>
+        </is>
+      </c>
+      <c r="D9" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E9" s="90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" s="90" t="inlineStr">
+        <is>
+          <t>🟡 권장</t>
+        </is>
+      </c>
+      <c r="G9" s="90" t="inlineStr">
+        <is>
+          <t>계정 활성화 상태 관리 — 탈퇴/정지 계정 처리용 (0=비활성)</t>
+        </is>
+      </c>
+      <c r="H9" s="90" t="inlineStr">
+        <is>
+          <t>회원 관리</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="100" t="inlineStr">
+        <is>
+          <t>🛠️  보완 ALTER TABLE SQL — 기존 테이블에 추가 실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="95" t="inlineStr">
+        <is>
+          <t>-- ① sns_comments 에 대댓글 컬럼 추가 (1차 필수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="94" t="inlineStr">
+        <is>
+          <t>ALTER TABLE sns_comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ADD COLUMN parent_comment_id INT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ADD CONSTRAINT fk_parent_comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (parent_comment_id) REFERENCES sns_comments(id) ON DELETE CASCADE;</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="94" t="inlineStr"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="95" t="inlineStr">
+        <is>
+          <t>-- ② sns_posts 에 수정일 컬럼 추가 (1차 필수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t>ALTER TABLE sns_posts ADD COLUMN updated_at DATETIME NULL ON UPDATE NOW();</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="94" t="inlineStr"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="95" t="inlineStr">
+        <is>
+          <t>-- ③ sns_users 에 수정일 + 활성화 컬럼 추가 (권장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="94" t="inlineStr">
+        <is>
+          <t>ALTER TABLE sns_users</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ADD COLUMN updated_at DATETIME  NULL         ON UPDATE NOW(),</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ADD COLUMN is_active  TINYINT(1) NOT NULL DEFAULT 1;</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="94" t="inlineStr"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="95" t="inlineStr">
+        <is>
+          <t>-- ④ sns_posts 에 소프트 삭제 컬럼 추가 (권장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="94" t="inlineStr">
+        <is>
+          <t>ALTER TABLE sns_posts ADD COLUMN is_deleted TINYINT(1) NOT NULL DEFAULT 0;</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="95" t="inlineStr">
+        <is>
+          <t>-- 소프트 삭제 시 조회: SELECT * FROM sns_posts WHERE is_deleted = 0;</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A19:H19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="101" t="inlineStr">
+        <is>
+          <t>🐾  PawLog SNS — 추가 DB 구조 요약 (Ver 2.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>기존 Ver 1.0 (3개 테이블) → 1차 필수 기능 완성을 위해 11개 테이블 추가 | 테이블 prefix: sns_</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="93" t="inlineStr">
+        <is>
+          <t>📦  기존 테이블 (Ver 1.0 — 변경 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="88" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="88" t="inlineStr">
+        <is>
+          <t>테이블명</t>
+        </is>
+      </c>
+      <c r="C5" s="88" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="D5" s="88" t="inlineStr">
+        <is>
+          <t>컬럼 수</t>
+        </is>
+      </c>
+      <c r="E5" s="88" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="F5" s="88" t="inlineStr">
+        <is>
+          <t>시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="89" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>sns_users</t>
+        </is>
+      </c>
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>사용자 계정 및 프로필</t>
+        </is>
+      </c>
+      <c r="D6" s="90" t="inlineStr">
+        <is>
+          <t>8개</t>
+        </is>
+      </c>
+      <c r="E6" s="90" t="inlineStr">
+        <is>
+          <t>핵심 테이블 — 모든 FK 참조 기준</t>
+        </is>
+      </c>
+      <c r="F6" s="90" t="inlineStr">
+        <is>
+          <t>👤 sns_users</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="91" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>sns_posts</t>
+        </is>
+      </c>
+      <c r="C7" s="92" t="inlineStr">
+        <is>
+          <t>게시물 정보</t>
+        </is>
+      </c>
+      <c r="D7" s="92" t="inlineStr">
+        <is>
+          <t>6개</t>
+        </is>
+      </c>
+      <c r="E7" s="92" t="inlineStr">
+        <is>
+          <t>Unsplash API 이미지 URL 저장</t>
+        </is>
+      </c>
+      <c r="F7" s="92" t="inlineStr">
+        <is>
+          <t>📷 sns_posts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="89" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B8" s="89" t="inlineStr">
+        <is>
+          <t>sns_comments</t>
+        </is>
+      </c>
+      <c r="C8" s="90" t="inlineStr">
+        <is>
+          <t>게시물 댓글</t>
+        </is>
+      </c>
+      <c r="D8" s="90" t="inlineStr">
+        <is>
+          <t>5개</t>
+        </is>
+      </c>
+      <c r="E8" s="90" t="inlineStr">
+        <is>
+          <t>posts, users 양방향 FK</t>
+        </is>
+      </c>
+      <c r="F8" s="90" t="inlineStr">
+        <is>
+          <t>💬 sns_comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="93" t="inlineStr">
+        <is>
+          <t>📦  추가 테이블 (Ver 2.0 — 1차 필수 기능 완성)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="88" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B11" s="88" t="inlineStr">
+        <is>
+          <t>테이블명</t>
+        </is>
+      </c>
+      <c r="C11" s="88" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="D11" s="88" t="inlineStr">
+        <is>
+          <t>컬럼 수</t>
+        </is>
+      </c>
+      <c r="E11" s="88" t="inlineStr">
+        <is>
+          <t>대응 필수 기능 (기획서)</t>
+        </is>
+      </c>
+      <c r="F11" s="88" t="inlineStr">
+        <is>
+          <t>시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="89" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B12" s="89" t="inlineStr">
+        <is>
+          <t>sns_follows</t>
+        </is>
+      </c>
+      <c r="C12" s="90" t="inlineStr">
+        <is>
+          <t>팔로우 / 팔로워 관계</t>
+        </is>
+      </c>
+      <c r="D12" s="90" t="inlineStr">
+        <is>
+          <t>4개</t>
+        </is>
+      </c>
+      <c r="E12" s="90" t="inlineStr">
+        <is>
+          <t>04 팔로우 시스템</t>
+        </is>
+      </c>
+      <c r="F12" s="90" t="inlineStr">
+        <is>
+          <t>👥 sns_follows</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="91" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B13" s="91" t="inlineStr">
+        <is>
+          <t>sns_stories</t>
+        </is>
+      </c>
+      <c r="C13" s="92" t="inlineStr">
+        <is>
+          <t>24시간 소멸 스토리</t>
+        </is>
+      </c>
+      <c r="D13" s="92" t="inlineStr">
+        <is>
+          <t>6개</t>
+        </is>
+      </c>
+      <c r="E13" s="92" t="inlineStr">
+        <is>
+          <t>02 피드 &amp; 스토리</t>
+        </is>
+      </c>
+      <c r="F13" s="92" t="inlineStr">
+        <is>
+          <t>📖 sns_stories</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="89" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B14" s="89" t="inlineStr">
+        <is>
+          <t>sns_story_views</t>
+        </is>
+      </c>
+      <c r="C14" s="90" t="inlineStr">
+        <is>
+          <t>스토리 조회자 기록</t>
+        </is>
+      </c>
+      <c r="D14" s="90" t="inlineStr">
+        <is>
+          <t>4개</t>
+        </is>
+      </c>
+      <c r="E14" s="90" t="inlineStr">
+        <is>
+          <t>02 피드 &amp; 스토리</t>
+        </is>
+      </c>
+      <c r="F14" s="90" t="inlineStr">
+        <is>
+          <t>👁 sns_story_views</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="91" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B15" s="91" t="inlineStr">
+        <is>
+          <t>sns_likes</t>
+        </is>
+      </c>
+      <c r="C15" s="92" t="inlineStr">
+        <is>
+          <t>게시물 좋아요 (사용자별)</t>
+        </is>
+      </c>
+      <c r="D15" s="92" t="inlineStr">
+        <is>
+          <t>4개</t>
+        </is>
+      </c>
+      <c r="E15" s="92" t="inlineStr">
+        <is>
+          <t>05 좋아요 &amp; 댓글</t>
+        </is>
+      </c>
+      <c r="F15" s="92" t="inlineStr">
+        <is>
+          <t>❤ sns_likes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="89" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B16" s="89" t="inlineStr">
+        <is>
+          <t>sns_post_images</t>
+        </is>
+      </c>
+      <c r="C16" s="90" t="inlineStr">
+        <is>
+          <t>게시물 다중 이미지 (최대 10장)</t>
+        </is>
+      </c>
+      <c r="D16" s="90" t="inlineStr">
+        <is>
+          <t>5개</t>
+        </is>
+      </c>
+      <c r="E16" s="90" t="inlineStr">
+        <is>
+          <t>03 게시물 CRUD</t>
+        </is>
+      </c>
+      <c r="F16" s="90" t="inlineStr">
+        <is>
+          <t>🖼 sns_post_images</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="91" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B17" s="91" t="inlineStr">
+        <is>
+          <t>sns_hashtags</t>
+        </is>
+      </c>
+      <c r="C17" s="92" t="inlineStr">
+        <is>
+          <t>해시태그 마스터</t>
+        </is>
+      </c>
+      <c r="D17" s="92" t="inlineStr">
+        <is>
+          <t>4개</t>
+        </is>
+      </c>
+      <c r="E17" s="92" t="inlineStr">
+        <is>
+          <t>03 게시물 CRUD + 탐색/검색</t>
+        </is>
+      </c>
+      <c r="F17" s="92" t="inlineStr">
+        <is>
+          <t>🏷 sns_hashtags</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="89" t="inlineStr">
+        <is>
+          <t>sns_post_hashtags</t>
+        </is>
+      </c>
+      <c r="C18" s="90" t="inlineStr">
+        <is>
+          <t>게시물-해시태그 M:N 연결</t>
+        </is>
+      </c>
+      <c r="D18" s="90" t="inlineStr">
+        <is>
+          <t>3개</t>
+        </is>
+      </c>
+      <c r="E18" s="90" t="inlineStr">
+        <is>
+          <t>03 게시물 CRUD + 탐색/검색</t>
+        </is>
+      </c>
+      <c r="F18" s="90" t="inlineStr">
+        <is>
+          <t>🔗 sns_post_hashtags</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="91" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="91" t="inlineStr">
+        <is>
+          <t>sns_pets</t>
+        </is>
+      </c>
+      <c r="C19" s="92" t="inlineStr">
+        <is>
+          <t>반려동물 프로필 (다두 지원)</t>
+        </is>
+      </c>
+      <c r="D19" s="92" t="inlineStr">
+        <is>
+          <t>9개</t>
+        </is>
+      </c>
+      <c r="E19" s="92" t="inlineStr">
+        <is>
+          <t>06 반려동물 프로필</t>
+        </is>
+      </c>
+      <c r="F19" s="92" t="inlineStr">
+        <is>
+          <t>🐾 sns_pets</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="89" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="89" t="inlineStr">
+        <is>
+          <t>sns_social_accounts</t>
+        </is>
+      </c>
+      <c r="C20" s="90" t="inlineStr">
+        <is>
+          <t>소셜 로그인 계정 연동</t>
+        </is>
+      </c>
+      <c r="D20" s="90" t="inlineStr">
+        <is>
+          <t>7개</t>
+        </is>
+      </c>
+      <c r="E20" s="90" t="inlineStr">
+        <is>
+          <t>01 소셜 로그인 (카카오/구글)</t>
+        </is>
+      </c>
+      <c r="F20" s="90" t="inlineStr">
+        <is>
+          <t>🔑 sns_social_accounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="91" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B21" s="91" t="inlineStr">
+        <is>
+          <t>sns_comment_reports</t>
+        </is>
+      </c>
+      <c r="C21" s="92" t="inlineStr">
+        <is>
+          <t>댓글 신고 기록</t>
+        </is>
+      </c>
+      <c r="D21" s="92" t="inlineStr">
+        <is>
+          <t>7개</t>
+        </is>
+      </c>
+      <c r="E21" s="92" t="inlineStr">
+        <is>
+          <t>05 좋아요 &amp; 댓글 (신고)</t>
+        </is>
+      </c>
+      <c r="F21" s="92" t="inlineStr">
+        <is>
+          <t>🚨 sns_comment_reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="89" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B22" s="89" t="inlineStr">
+        <is>
+          <t>sns_post_pet_tags</t>
+        </is>
+      </c>
+      <c r="C22" s="90" t="inlineStr">
+        <is>
+          <t>게시물-반려동물 태그 M:N 연결</t>
+        </is>
+      </c>
+      <c r="D22" s="90" t="inlineStr">
+        <is>
+          <t>3개</t>
+        </is>
+      </c>
+      <c r="E22" s="90" t="inlineStr">
+        <is>
+          <t>03 게시물 CRUD (반려동물 태그)</t>
+        </is>
+      </c>
+      <c r="F22" s="90" t="inlineStr">
+        <is>
+          <t>🐶 sns_post_pet_tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="93" t="inlineStr">
+        <is>
+          <t>🔗  추가 테이블 관계 요약 (ERD 간략)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="88" t="inlineStr">
+        <is>
+          <t>부모 테이블</t>
+        </is>
+      </c>
+      <c r="B26" s="88" t="inlineStr">
+        <is>
+          <t>관계</t>
+        </is>
+      </c>
+      <c r="C26" s="88" t="inlineStr">
+        <is>
+          <t>자식 테이블</t>
+        </is>
+      </c>
+      <c r="D26" s="88" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E26" s="88" t="inlineStr">
+        <is>
+          <t>FK 연결</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="89" t="inlineStr">
+        <is>
+          <t>sns_users</t>
+        </is>
+      </c>
+      <c r="B27" s="90" t="inlineStr">
+        <is>
+          <t>1 : N</t>
+        </is>
+      </c>
+      <c r="C27" s="90" t="inlineStr">
+        <is>
+          <t>sns_follows</t>
+        </is>
+      </c>
+      <c r="D27" s="90" t="inlineStr">
+        <is>
+          <t>팔로워/팔로잉 관계</t>
+        </is>
+      </c>
+      <c r="E27" s="90" t="inlineStr">
+        <is>
+          <t>follower_id / following_id → sns_users.id</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="91" t="inlineStr">
+        <is>
+          <t>sns_users</t>
+        </is>
+      </c>
+      <c r="B28" s="92" t="inlineStr">
+        <is>
+          <t>1 : N</t>
+        </is>
+      </c>
+      <c r="C28" s="92" t="inlineStr">
+        <is>
+          <t>sns_stories</t>
+        </is>
+      </c>
+      <c r="D28" s="92" t="inlineStr">
+        <is>
+          <t>사용자가 여러 스토리 작성</t>
+        </is>
+      </c>
+      <c r="E28" s="92" t="inlineStr">
+        <is>
+          <t>sns_stories.user_id → sns_users.id</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="89" t="inlineStr">
+        <is>
+          <t>sns_stories</t>
+        </is>
+      </c>
+      <c r="B29" s="90" t="inlineStr">
+        <is>
+          <t>1 : N</t>
+        </is>
+      </c>
+      <c r="C29" s="90" t="inlineStr">
+        <is>
+          <t>sns_story_views</t>
+        </is>
+      </c>
+      <c r="D29" s="90" t="inlineStr">
+        <is>
+          <t>스토리 조회자 기록</t>
+        </is>
+      </c>
+      <c r="E29" s="90" t="inlineStr">
+        <is>
+          <t>sns_story_views.story_id → sns_stories.id</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="91" t="inlineStr">
+        <is>
+          <t>sns_users</t>
+        </is>
+      </c>
+      <c r="B30" s="92" t="inlineStr">
+        <is>
+          <t>1 : N</t>
+        </is>
+      </c>
+      <c r="C30" s="92" t="inlineStr">
+        <is>
+          <t>sns_likes</t>
+        </is>
+      </c>
+      <c r="D30" s="92" t="inlineStr">
+        <is>
+          <t>사용자가 여러 게시물 좋아요</t>
+        </is>
+      </c>
+      <c r="E30" s="92" t="inlineStr">
+        <is>
+          <t>sns_likes.user_id → sns_users.id</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="89" t="inlineStr">
+        <is>
+          <t>sns_posts</t>
+        </is>
+      </c>
+      <c r="B31" s="90" t="inlineStr">
+        <is>
+          <t>1 : N</t>
+        </is>
+      </c>
+      <c r="C31" s="90" t="inlineStr">
+        <is>
+          <t>sns_likes</t>
+        </is>
+      </c>
+      <c r="D31" s="90" t="inlineStr">
+        <is>
+          <t>게시물이 여러 좋아요 보유</t>
+        </is>
+      </c>
+      <c r="E31" s="90" t="inlineStr">
+        <is>
+          <t>sns_likes.post_id → sns_posts.id</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="91" t="inlineStr">
+        <is>
+          <t>sns_posts</t>
+        </is>
+      </c>
+      <c r="B32" s="92" t="inlineStr">
+        <is>
+          <t>1 : N</t>
+        </is>
+      </c>
+      <c r="C32" s="92" t="inlineStr">
+        <is>
+          <t>sns_post_images</t>
+        </is>
+      </c>
+      <c r="D32" s="92" t="inlineStr">
+        <is>
+          <t>게시물에 여러 이미지 연결</t>
+        </is>
+      </c>
+      <c r="E32" s="92" t="inlineStr">
+        <is>
+          <t>sns_post_images.post_id → sns_posts.id</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="89" t="inlineStr">
+        <is>
+          <t>sns_posts</t>
+        </is>
+      </c>
+      <c r="B33" s="90" t="inlineStr">
+        <is>
+          <t>M : N</t>
+        </is>
+      </c>
+      <c r="C33" s="90" t="inlineStr">
+        <is>
+          <t>sns_hashtags</t>
+        </is>
+      </c>
+      <c r="D33" s="90" t="inlineStr">
+        <is>
+          <t>중간: sns_post_hashtags</t>
+        </is>
+      </c>
+      <c r="E33" s="90" t="inlineStr">
+        <is>
+          <t>post_id / hashtag_id FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="91" t="inlineStr">
+        <is>
+          <t>sns_users</t>
+        </is>
+      </c>
+      <c r="B34" s="92" t="inlineStr">
+        <is>
+          <t>1 : N</t>
+        </is>
+      </c>
+      <c r="C34" s="92" t="inlineStr">
+        <is>
+          <t>sns_pets</t>
+        </is>
+      </c>
+      <c r="D34" s="92" t="inlineStr">
+        <is>
+          <t>사용자가 여러 반려동물 등록</t>
+        </is>
+      </c>
+      <c r="E34" s="92" t="inlineStr">
+        <is>
+          <t>sns_pets.user_id → sns_users.id</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="89" t="inlineStr">
+        <is>
+          <t>sns_users</t>
+        </is>
+      </c>
+      <c r="B35" s="90" t="inlineStr">
+        <is>
+          <t>1 : N</t>
+        </is>
+      </c>
+      <c r="C35" s="90" t="inlineStr">
+        <is>
+          <t>sns_social_accounts</t>
+        </is>
+      </c>
+      <c r="D35" s="90" t="inlineStr">
+        <is>
+          <t>소셜 계정 연결 (카카오/구글)</t>
+        </is>
+      </c>
+      <c r="E35" s="90" t="inlineStr">
+        <is>
+          <t>sns_social_accounts.user_id → sns_users.id</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="91" t="inlineStr">
+        <is>
+          <t>sns_posts</t>
+        </is>
+      </c>
+      <c r="B36" s="92" t="inlineStr">
+        <is>
+          <t>M : N</t>
+        </is>
+      </c>
+      <c r="C36" s="92" t="inlineStr">
+        <is>
+          <t>sns_pets</t>
+        </is>
+      </c>
+      <c r="D36" s="92" t="inlineStr">
+        <is>
+          <t>중간: sns_post_pet_tags</t>
+        </is>
+      </c>
+      <c r="E36" s="92" t="inlineStr">
+        <is>
+          <t>post_id / pet_id FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="89" t="inlineStr">
+        <is>
+          <t>sns_comments</t>
+        </is>
+      </c>
+      <c r="B37" s="90" t="inlineStr">
+        <is>
+          <t>1 : N</t>
+        </is>
+      </c>
+      <c r="C37" s="90" t="inlineStr">
+        <is>
+          <t>sns_comment_reports</t>
+        </is>
+      </c>
+      <c r="D37" s="90" t="inlineStr">
+        <is>
+          <t>댓글 신고 기록</t>
+        </is>
+      </c>
+      <c r="E37" s="90" t="inlineStr">
+        <is>
+          <t>sns_comment_reports.comment_id → sns_comments.id</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="91" t="inlineStr">
+        <is>
+          <t>sns_comments</t>
+        </is>
+      </c>
+      <c r="B38" s="92" t="inlineStr">
+        <is>
+          <t>자기 참조</t>
+        </is>
+      </c>
+      <c r="C38" s="92" t="inlineStr">
+        <is>
+          <t>sns_comments</t>
+        </is>
+      </c>
+      <c r="D38" s="92" t="inlineStr">
+        <is>
+          <t>대댓글 (ALTER TABLE 보완)</t>
+        </is>
+      </c>
+      <c r="E38" s="92" t="inlineStr">
+        <is>
+          <t>parent_comment_id → sns_comments.id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1314,6 +5867,13 @@
           <t>👤  테이블: sns_users   —   사용자 계정 및 프로필 정보</t>
         </is>
       </c>
+      <c r="B2" s="84" t="n"/>
+      <c r="C2" s="84" t="n"/>
+      <c r="D2" s="84" t="n"/>
+      <c r="E2" s="84" t="n"/>
+      <c r="F2" s="84" t="n"/>
+      <c r="G2" s="84" t="n"/>
+      <c r="H2" s="85" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
@@ -1321,6 +5881,13 @@
           <t>SNS 로그인 / 회원가입 / 프로필 화면에서 필요한 정보를 저장하는 핵심 테이블</t>
         </is>
       </c>
+      <c r="B3" s="84" t="n"/>
+      <c r="C3" s="84" t="n"/>
+      <c r="D3" s="84" t="n"/>
+      <c r="E3" s="84" t="n"/>
+      <c r="F3" s="84" t="n"/>
+      <c r="G3" s="84" t="n"/>
+      <c r="H3" s="85" t="n"/>
     </row>
     <row r="4" ht="14" customHeight="1"/>
     <row r="5" ht="24" customHeight="1">
@@ -1708,6 +6275,13 @@
           <t>🛠️  CREATE TABLE SQL</t>
         </is>
       </c>
+      <c r="B16" s="84" t="n"/>
+      <c r="C16" s="84" t="n"/>
+      <c r="D16" s="84" t="n"/>
+      <c r="E16" s="84" t="n"/>
+      <c r="F16" s="84" t="n"/>
+      <c r="G16" s="84" t="n"/>
+      <c r="H16" s="85" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="53" t="inlineStr">
@@ -1715,6 +6289,13 @@
           <t>CREATE TABLE sns_users (</t>
         </is>
       </c>
+      <c r="B17" s="84" t="n"/>
+      <c r="C17" s="84" t="n"/>
+      <c r="D17" s="84" t="n"/>
+      <c r="E17" s="84" t="n"/>
+      <c r="F17" s="84" t="n"/>
+      <c r="G17" s="84" t="n"/>
+      <c r="H17" s="85" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="54" t="inlineStr">
@@ -1722,6 +6303,13 @@
           <t xml:space="preserve">    id           INT           NOT NULL AUTO_INCREMENT,</t>
         </is>
       </c>
+      <c r="B18" s="84" t="n"/>
+      <c r="C18" s="84" t="n"/>
+      <c r="D18" s="84" t="n"/>
+      <c r="E18" s="84" t="n"/>
+      <c r="F18" s="84" t="n"/>
+      <c r="G18" s="84" t="n"/>
+      <c r="H18" s="85" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="54" t="inlineStr">
@@ -1729,6 +6317,13 @@
           <t xml:space="preserve">    username     VARCHAR(50)   NOT NULL,</t>
         </is>
       </c>
+      <c r="B19" s="84" t="n"/>
+      <c r="C19" s="84" t="n"/>
+      <c r="D19" s="84" t="n"/>
+      <c r="E19" s="84" t="n"/>
+      <c r="F19" s="84" t="n"/>
+      <c r="G19" s="84" t="n"/>
+      <c r="H19" s="85" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="54" t="inlineStr">
@@ -1736,6 +6331,13 @@
           <t xml:space="preserve">    email        VARCHAR(100)  NOT NULL,</t>
         </is>
       </c>
+      <c r="B20" s="84" t="n"/>
+      <c r="C20" s="84" t="n"/>
+      <c r="D20" s="84" t="n"/>
+      <c r="E20" s="84" t="n"/>
+      <c r="F20" s="84" t="n"/>
+      <c r="G20" s="84" t="n"/>
+      <c r="H20" s="85" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="54" t="inlineStr">
@@ -1743,6 +6345,13 @@
           <t xml:space="preserve">    password     VARCHAR(255)  NOT NULL,</t>
         </is>
       </c>
+      <c r="B21" s="84" t="n"/>
+      <c r="C21" s="84" t="n"/>
+      <c r="D21" s="84" t="n"/>
+      <c r="E21" s="84" t="n"/>
+      <c r="F21" s="84" t="n"/>
+      <c r="G21" s="84" t="n"/>
+      <c r="H21" s="85" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="54" t="inlineStr">
@@ -1750,6 +6359,13 @@
           <t xml:space="preserve">    display_name VARCHAR(100)  NOT NULL,</t>
         </is>
       </c>
+      <c r="B22" s="84" t="n"/>
+      <c r="C22" s="84" t="n"/>
+      <c r="D22" s="84" t="n"/>
+      <c r="E22" s="84" t="n"/>
+      <c r="F22" s="84" t="n"/>
+      <c r="G22" s="84" t="n"/>
+      <c r="H22" s="85" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="54" t="inlineStr">
@@ -1757,6 +6373,13 @@
           <t xml:space="preserve">    bio          TEXT          NULL,</t>
         </is>
       </c>
+      <c r="B23" s="84" t="n"/>
+      <c r="C23" s="84" t="n"/>
+      <c r="D23" s="84" t="n"/>
+      <c r="E23" s="84" t="n"/>
+      <c r="F23" s="84" t="n"/>
+      <c r="G23" s="84" t="n"/>
+      <c r="H23" s="85" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="54" t="inlineStr">
@@ -1764,6 +6387,13 @@
           <t xml:space="preserve">    profile_image VARCHAR(300) NULL,</t>
         </is>
       </c>
+      <c r="B24" s="84" t="n"/>
+      <c r="C24" s="84" t="n"/>
+      <c r="D24" s="84" t="n"/>
+      <c r="E24" s="84" t="n"/>
+      <c r="F24" s="84" t="n"/>
+      <c r="G24" s="84" t="n"/>
+      <c r="H24" s="85" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="54" t="inlineStr">
@@ -1771,6 +6401,13 @@
           <t xml:space="preserve">    created_at   DATETIME      NOT NULL DEFAULT NOW(),</t>
         </is>
       </c>
+      <c r="B25" s="84" t="n"/>
+      <c r="C25" s="84" t="n"/>
+      <c r="D25" s="84" t="n"/>
+      <c r="E25" s="84" t="n"/>
+      <c r="F25" s="84" t="n"/>
+      <c r="G25" s="84" t="n"/>
+      <c r="H25" s="85" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="55" t="inlineStr">
@@ -1778,6 +6415,13 @@
           <t xml:space="preserve">    PRIMARY KEY (id),</t>
         </is>
       </c>
+      <c r="B26" s="84" t="n"/>
+      <c r="C26" s="84" t="n"/>
+      <c r="D26" s="84" t="n"/>
+      <c r="E26" s="84" t="n"/>
+      <c r="F26" s="84" t="n"/>
+      <c r="G26" s="84" t="n"/>
+      <c r="H26" s="85" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="55" t="inlineStr">
@@ -1785,6 +6429,13 @@
           <t xml:space="preserve">    UNIQUE KEY uq_username (username),</t>
         </is>
       </c>
+      <c r="B27" s="84" t="n"/>
+      <c r="C27" s="84" t="n"/>
+      <c r="D27" s="84" t="n"/>
+      <c r="E27" s="84" t="n"/>
+      <c r="F27" s="84" t="n"/>
+      <c r="G27" s="84" t="n"/>
+      <c r="H27" s="85" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="55" t="inlineStr">
@@ -1792,6 +6443,13 @@
           <t xml:space="preserve">    UNIQUE KEY uq_email    (email)</t>
         </is>
       </c>
+      <c r="B28" s="84" t="n"/>
+      <c r="C28" s="84" t="n"/>
+      <c r="D28" s="84" t="n"/>
+      <c r="E28" s="84" t="n"/>
+      <c r="F28" s="84" t="n"/>
+      <c r="G28" s="84" t="n"/>
+      <c r="H28" s="85" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="56" t="inlineStr">
@@ -1799,13 +6457,20 @@
           <t>);</t>
         </is>
       </c>
+      <c r="B29" s="84" t="n"/>
+      <c r="C29" s="84" t="n"/>
+      <c r="D29" s="84" t="n"/>
+      <c r="E29" s="84" t="n"/>
+      <c r="F29" s="84" t="n"/>
+      <c r="G29" s="84" t="n"/>
+      <c r="H29" s="85" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A20:H20"/>
@@ -1848,6 +6513,13 @@
           <t>📷  테이블: sns_posts   —   게시물 정보</t>
         </is>
       </c>
+      <c r="B2" s="84" t="n"/>
+      <c r="C2" s="84" t="n"/>
+      <c r="D2" s="84" t="n"/>
+      <c r="E2" s="84" t="n"/>
+      <c r="F2" s="84" t="n"/>
+      <c r="G2" s="84" t="n"/>
+      <c r="H2" s="85" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
@@ -1855,6 +6527,13 @@
           <t>SNS 피드 화면에서 필요한 게시물 정보 저장 | 이미지는 Unsplash API URL로 저장</t>
         </is>
       </c>
+      <c r="B3" s="84" t="n"/>
+      <c r="C3" s="84" t="n"/>
+      <c r="D3" s="84" t="n"/>
+      <c r="E3" s="84" t="n"/>
+      <c r="F3" s="84" t="n"/>
+      <c r="G3" s="84" t="n"/>
+      <c r="H3" s="85" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
@@ -2157,6 +6836,13 @@
           <t>📝  게시물 작성 4단계 흐름 (Unsplash API 연동)</t>
         </is>
       </c>
+      <c r="B14" s="84" t="n"/>
+      <c r="C14" s="84" t="n"/>
+      <c r="D14" s="84" t="n"/>
+      <c r="E14" s="84" t="n"/>
+      <c r="F14" s="84" t="n"/>
+      <c r="G14" s="84" t="n"/>
+      <c r="H14" s="85" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -2191,6 +6877,11 @@
           <t>사용자가 게시물 본문(caption) 텍스트 입력. 해시태그 # 자동 파싱.</t>
         </is>
       </c>
+      <c r="D16" s="84" t="n"/>
+      <c r="E16" s="84" t="n"/>
+      <c r="F16" s="84" t="n"/>
+      <c r="G16" s="84" t="n"/>
+      <c r="H16" s="85" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="66" t="inlineStr">
@@ -2208,6 +6899,11 @@
           <t>Unsplash API 호출 → 랜덤 이미지 그리드로 표시 (여러 장 미리보기).</t>
         </is>
       </c>
+      <c r="D17" s="84" t="n"/>
+      <c r="E17" s="84" t="n"/>
+      <c r="F17" s="84" t="n"/>
+      <c r="G17" s="84" t="n"/>
+      <c r="H17" s="85" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="65" t="inlineStr">
@@ -2225,6 +6921,11 @@
           <t>마음에 드는 이미지 클릭 선택. '새로고침'으로 다른 랜덤 이미지 재요청 가능.</t>
         </is>
       </c>
+      <c r="D18" s="84" t="n"/>
+      <c r="E18" s="84" t="n"/>
+      <c r="F18" s="84" t="n"/>
+      <c r="G18" s="84" t="n"/>
+      <c r="H18" s="85" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="66" t="inlineStr">
@@ -2242,6 +6943,11 @@
           <t>선택한 Unsplash 이미지의 URL → sns_posts.image_url 필드에 저장 후 게시.</t>
         </is>
       </c>
+      <c r="D19" s="84" t="n"/>
+      <c r="E19" s="84" t="n"/>
+      <c r="F19" s="84" t="n"/>
+      <c r="G19" s="84" t="n"/>
+      <c r="H19" s="85" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="52" t="inlineStr">
@@ -2249,6 +6955,13 @@
           <t>🛠️  CREATE TABLE SQL</t>
         </is>
       </c>
+      <c r="B21" s="84" t="n"/>
+      <c r="C21" s="84" t="n"/>
+      <c r="D21" s="84" t="n"/>
+      <c r="E21" s="84" t="n"/>
+      <c r="F21" s="84" t="n"/>
+      <c r="G21" s="84" t="n"/>
+      <c r="H21" s="85" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="53" t="inlineStr">
@@ -2256,6 +6969,13 @@
           <t>CREATE TABLE sns_posts (</t>
         </is>
       </c>
+      <c r="B22" s="84" t="n"/>
+      <c r="C22" s="84" t="n"/>
+      <c r="D22" s="84" t="n"/>
+      <c r="E22" s="84" t="n"/>
+      <c r="F22" s="84" t="n"/>
+      <c r="G22" s="84" t="n"/>
+      <c r="H22" s="85" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="54" t="inlineStr">
@@ -2263,6 +6983,13 @@
           <t xml:space="preserve">    id          INT           NOT NULL AUTO_INCREMENT,</t>
         </is>
       </c>
+      <c r="B23" s="84" t="n"/>
+      <c r="C23" s="84" t="n"/>
+      <c r="D23" s="84" t="n"/>
+      <c r="E23" s="84" t="n"/>
+      <c r="F23" s="84" t="n"/>
+      <c r="G23" s="84" t="n"/>
+      <c r="H23" s="85" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="54" t="inlineStr">
@@ -2270,6 +6997,13 @@
           <t xml:space="preserve">    user_id     INT           NOT NULL,</t>
         </is>
       </c>
+      <c r="B24" s="84" t="n"/>
+      <c r="C24" s="84" t="n"/>
+      <c r="D24" s="84" t="n"/>
+      <c r="E24" s="84" t="n"/>
+      <c r="F24" s="84" t="n"/>
+      <c r="G24" s="84" t="n"/>
+      <c r="H24" s="85" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="54" t="inlineStr">
@@ -2277,6 +7011,13 @@
           <t xml:space="preserve">    caption     TEXT          NULL,</t>
         </is>
       </c>
+      <c r="B25" s="84" t="n"/>
+      <c r="C25" s="84" t="n"/>
+      <c r="D25" s="84" t="n"/>
+      <c r="E25" s="84" t="n"/>
+      <c r="F25" s="84" t="n"/>
+      <c r="G25" s="84" t="n"/>
+      <c r="H25" s="85" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="54" t="inlineStr">
@@ -2284,6 +7025,13 @@
           <t xml:space="preserve">    image_url   VARCHAR(500)  NULL,</t>
         </is>
       </c>
+      <c r="B26" s="84" t="n"/>
+      <c r="C26" s="84" t="n"/>
+      <c r="D26" s="84" t="n"/>
+      <c r="E26" s="84" t="n"/>
+      <c r="F26" s="84" t="n"/>
+      <c r="G26" s="84" t="n"/>
+      <c r="H26" s="85" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="54" t="inlineStr">
@@ -2291,6 +7039,13 @@
           <t xml:space="preserve">    likes_count INT           NOT NULL DEFAULT 0,</t>
         </is>
       </c>
+      <c r="B27" s="84" t="n"/>
+      <c r="C27" s="84" t="n"/>
+      <c r="D27" s="84" t="n"/>
+      <c r="E27" s="84" t="n"/>
+      <c r="F27" s="84" t="n"/>
+      <c r="G27" s="84" t="n"/>
+      <c r="H27" s="85" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="54" t="inlineStr">
@@ -2298,6 +7053,13 @@
           <t xml:space="preserve">    created_at  DATETIME      NOT NULL DEFAULT NOW(),</t>
         </is>
       </c>
+      <c r="B28" s="84" t="n"/>
+      <c r="C28" s="84" t="n"/>
+      <c r="D28" s="84" t="n"/>
+      <c r="E28" s="84" t="n"/>
+      <c r="F28" s="84" t="n"/>
+      <c r="G28" s="84" t="n"/>
+      <c r="H28" s="85" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="55" t="inlineStr">
@@ -2305,6 +7067,13 @@
           <t xml:space="preserve">    PRIMARY KEY (id),</t>
         </is>
       </c>
+      <c r="B29" s="84" t="n"/>
+      <c r="C29" s="84" t="n"/>
+      <c r="D29" s="84" t="n"/>
+      <c r="E29" s="84" t="n"/>
+      <c r="F29" s="84" t="n"/>
+      <c r="G29" s="84" t="n"/>
+      <c r="H29" s="85" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="55" t="inlineStr">
@@ -2312,6 +7081,13 @@
           <t xml:space="preserve">    INDEX idx_user_id (user_id),</t>
         </is>
       </c>
+      <c r="B30" s="84" t="n"/>
+      <c r="C30" s="84" t="n"/>
+      <c r="D30" s="84" t="n"/>
+      <c r="E30" s="84" t="n"/>
+      <c r="F30" s="84" t="n"/>
+      <c r="G30" s="84" t="n"/>
+      <c r="H30" s="85" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="55" t="inlineStr">
@@ -2319,6 +7095,13 @@
           <t xml:space="preserve">    INDEX idx_created_at (created_at),</t>
         </is>
       </c>
+      <c r="B31" s="84" t="n"/>
+      <c r="C31" s="84" t="n"/>
+      <c r="D31" s="84" t="n"/>
+      <c r="E31" s="84" t="n"/>
+      <c r="F31" s="84" t="n"/>
+      <c r="G31" s="84" t="n"/>
+      <c r="H31" s="85" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="55" t="inlineStr">
@@ -2326,6 +7109,13 @@
           <t xml:space="preserve">    FOREIGN KEY (user_id) REFERENCES sns_users(id) ON DELETE CASCADE</t>
         </is>
       </c>
+      <c r="B32" s="84" t="n"/>
+      <c r="C32" s="84" t="n"/>
+      <c r="D32" s="84" t="n"/>
+      <c r="E32" s="84" t="n"/>
+      <c r="F32" s="84" t="n"/>
+      <c r="G32" s="84" t="n"/>
+      <c r="H32" s="85" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="56" t="inlineStr">
@@ -2333,6 +7123,13 @@
           <t>);</t>
         </is>
       </c>
+      <c r="B33" s="84" t="n"/>
+      <c r="C33" s="84" t="n"/>
+      <c r="D33" s="84" t="n"/>
+      <c r="E33" s="84" t="n"/>
+      <c r="F33" s="84" t="n"/>
+      <c r="G33" s="84" t="n"/>
+      <c r="H33" s="85" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -2386,6 +7183,13 @@
           <t>💬  테이블: sns_comments   —   게시물 댓글 정보</t>
         </is>
       </c>
+      <c r="B2" s="84" t="n"/>
+      <c r="C2" s="84" t="n"/>
+      <c r="D2" s="84" t="n"/>
+      <c r="E2" s="84" t="n"/>
+      <c r="F2" s="84" t="n"/>
+      <c r="G2" s="84" t="n"/>
+      <c r="H2" s="85" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
@@ -2393,6 +7197,13 @@
           <t>게시물 댓글 저장 테이블 | sns_users(댓글 작성자) 및 sns_posts(대상 게시물) 양방향 FK 연결</t>
         </is>
       </c>
+      <c r="B3" s="84" t="n"/>
+      <c r="C3" s="84" t="n"/>
+      <c r="D3" s="84" t="n"/>
+      <c r="E3" s="84" t="n"/>
+      <c r="F3" s="84" t="n"/>
+      <c r="G3" s="84" t="n"/>
+      <c r="H3" s="85" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
@@ -2652,6 +7463,13 @@
           <t>🛠️  CREATE TABLE SQL</t>
         </is>
       </c>
+      <c r="B13" s="84" t="n"/>
+      <c r="C13" s="84" t="n"/>
+      <c r="D13" s="84" t="n"/>
+      <c r="E13" s="84" t="n"/>
+      <c r="F13" s="84" t="n"/>
+      <c r="G13" s="84" t="n"/>
+      <c r="H13" s="85" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="53" t="inlineStr">
@@ -2659,6 +7477,13 @@
           <t>CREATE TABLE sns_comments (</t>
         </is>
       </c>
+      <c r="B14" s="84" t="n"/>
+      <c r="C14" s="84" t="n"/>
+      <c r="D14" s="84" t="n"/>
+      <c r="E14" s="84" t="n"/>
+      <c r="F14" s="84" t="n"/>
+      <c r="G14" s="84" t="n"/>
+      <c r="H14" s="85" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="54" t="inlineStr">
@@ -2666,6 +7491,13 @@
           <t xml:space="preserve">    id         INT       NOT NULL AUTO_INCREMENT,</t>
         </is>
       </c>
+      <c r="B15" s="84" t="n"/>
+      <c r="C15" s="84" t="n"/>
+      <c r="D15" s="84" t="n"/>
+      <c r="E15" s="84" t="n"/>
+      <c r="F15" s="84" t="n"/>
+      <c r="G15" s="84" t="n"/>
+      <c r="H15" s="85" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="54" t="inlineStr">
@@ -2673,6 +7505,13 @@
           <t xml:space="preserve">    content    TEXT      NOT NULL,</t>
         </is>
       </c>
+      <c r="B16" s="84" t="n"/>
+      <c r="C16" s="84" t="n"/>
+      <c r="D16" s="84" t="n"/>
+      <c r="E16" s="84" t="n"/>
+      <c r="F16" s="84" t="n"/>
+      <c r="G16" s="84" t="n"/>
+      <c r="H16" s="85" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="54" t="inlineStr">
@@ -2680,6 +7519,13 @@
           <t xml:space="preserve">    user_id    INT       NOT NULL,</t>
         </is>
       </c>
+      <c r="B17" s="84" t="n"/>
+      <c r="C17" s="84" t="n"/>
+      <c r="D17" s="84" t="n"/>
+      <c r="E17" s="84" t="n"/>
+      <c r="F17" s="84" t="n"/>
+      <c r="G17" s="84" t="n"/>
+      <c r="H17" s="85" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="54" t="inlineStr">
@@ -2687,6 +7533,13 @@
           <t xml:space="preserve">    post_id    INT       NOT NULL,</t>
         </is>
       </c>
+      <c r="B18" s="84" t="n"/>
+      <c r="C18" s="84" t="n"/>
+      <c r="D18" s="84" t="n"/>
+      <c r="E18" s="84" t="n"/>
+      <c r="F18" s="84" t="n"/>
+      <c r="G18" s="84" t="n"/>
+      <c r="H18" s="85" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="54" t="inlineStr">
@@ -2694,6 +7547,13 @@
           <t xml:space="preserve">    created_at DATETIME  NOT NULL DEFAULT NOW(),</t>
         </is>
       </c>
+      <c r="B19" s="84" t="n"/>
+      <c r="C19" s="84" t="n"/>
+      <c r="D19" s="84" t="n"/>
+      <c r="E19" s="84" t="n"/>
+      <c r="F19" s="84" t="n"/>
+      <c r="G19" s="84" t="n"/>
+      <c r="H19" s="85" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="55" t="inlineStr">
@@ -2701,6 +7561,13 @@
           <t xml:space="preserve">    PRIMARY KEY (id),</t>
         </is>
       </c>
+      <c r="B20" s="84" t="n"/>
+      <c r="C20" s="84" t="n"/>
+      <c r="D20" s="84" t="n"/>
+      <c r="E20" s="84" t="n"/>
+      <c r="F20" s="84" t="n"/>
+      <c r="G20" s="84" t="n"/>
+      <c r="H20" s="85" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="55" t="inlineStr">
@@ -2708,6 +7575,13 @@
           <t xml:space="preserve">    INDEX idx_post_id  (post_id),</t>
         </is>
       </c>
+      <c r="B21" s="84" t="n"/>
+      <c r="C21" s="84" t="n"/>
+      <c r="D21" s="84" t="n"/>
+      <c r="E21" s="84" t="n"/>
+      <c r="F21" s="84" t="n"/>
+      <c r="G21" s="84" t="n"/>
+      <c r="H21" s="85" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="55" t="inlineStr">
@@ -2715,6 +7589,13 @@
           <t xml:space="preserve">    INDEX idx_user_id  (user_id),</t>
         </is>
       </c>
+      <c r="B22" s="84" t="n"/>
+      <c r="C22" s="84" t="n"/>
+      <c r="D22" s="84" t="n"/>
+      <c r="E22" s="84" t="n"/>
+      <c r="F22" s="84" t="n"/>
+      <c r="G22" s="84" t="n"/>
+      <c r="H22" s="85" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="55" t="inlineStr">
@@ -2722,6 +7603,13 @@
           <t xml:space="preserve">    FOREIGN KEY (user_id) REFERENCES sns_users(id) ON DELETE CASCADE,</t>
         </is>
       </c>
+      <c r="B23" s="84" t="n"/>
+      <c r="C23" s="84" t="n"/>
+      <c r="D23" s="84" t="n"/>
+      <c r="E23" s="84" t="n"/>
+      <c r="F23" s="84" t="n"/>
+      <c r="G23" s="84" t="n"/>
+      <c r="H23" s="85" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="55" t="inlineStr">
@@ -2729,6 +7617,13 @@
           <t xml:space="preserve">    FOREIGN KEY (post_id) REFERENCES sns_posts(id) ON DELETE CASCADE</t>
         </is>
       </c>
+      <c r="B24" s="84" t="n"/>
+      <c r="C24" s="84" t="n"/>
+      <c r="D24" s="84" t="n"/>
+      <c r="E24" s="84" t="n"/>
+      <c r="F24" s="84" t="n"/>
+      <c r="G24" s="84" t="n"/>
+      <c r="H24" s="85" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="56" t="inlineStr">
@@ -2736,6 +7631,13 @@
           <t>);</t>
         </is>
       </c>
+      <c r="B25" s="84" t="n"/>
+      <c r="C25" s="84" t="n"/>
+      <c r="D25" s="84" t="n"/>
+      <c r="E25" s="84" t="n"/>
+      <c r="F25" s="84" t="n"/>
+      <c r="G25" s="84" t="n"/>
+      <c r="H25" s="85" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -2786,6 +7688,15 @@
           <t>🗺️  ERD 다이어그램  —  PawLog SNS 테이블 관계도</t>
         </is>
       </c>
+      <c r="B2" s="84" t="n"/>
+      <c r="C2" s="84" t="n"/>
+      <c r="D2" s="84" t="n"/>
+      <c r="E2" s="84" t="n"/>
+      <c r="F2" s="84" t="n"/>
+      <c r="G2" s="84" t="n"/>
+      <c r="H2" s="84" t="n"/>
+      <c r="I2" s="84" t="n"/>
+      <c r="J2" s="85" t="n"/>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -2793,11 +7704,17 @@
           <t xml:space="preserve">  sns_users</t>
         </is>
       </c>
+      <c r="B5" s="84" t="n"/>
+      <c r="C5" s="84" t="n"/>
+      <c r="D5" s="85" t="n"/>
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  sns_posts</t>
         </is>
       </c>
+      <c r="G5" s="84" t="n"/>
+      <c r="H5" s="84" t="n"/>
+      <c r="I5" s="85" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1">
       <c r="A6" s="67" t="inlineStr">
@@ -3009,6 +7926,9 @@
           <t xml:space="preserve">  sns_comments</t>
         </is>
       </c>
+      <c r="G14" s="84" t="n"/>
+      <c r="H14" s="84" t="n"/>
+      <c r="I14" s="85" t="n"/>
     </row>
     <row r="15" ht="14" customHeight="1">
       <c r="F15" s="67" t="inlineStr">
@@ -3034,6 +7954,15 @@
           <t>🔗  관계 설명</t>
         </is>
       </c>
+      <c r="B16" s="84" t="n"/>
+      <c r="C16" s="84" t="n"/>
+      <c r="D16" s="84" t="n"/>
+      <c r="E16" s="84" t="n"/>
+      <c r="F16" s="84" t="n"/>
+      <c r="G16" s="84" t="n"/>
+      <c r="H16" s="84" t="n"/>
+      <c r="I16" s="84" t="n"/>
+      <c r="J16" s="85" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
@@ -3046,6 +7975,8 @@
           <t>──────── 1 : N ────────▶</t>
         </is>
       </c>
+      <c r="C17" s="84" t="n"/>
+      <c r="D17" s="85" t="n"/>
       <c r="E17" s="76" t="inlineStr">
         <is>
           <t>sns_posts.user_id</t>
@@ -3056,10 +7987,10 @@
           <t>한 사용자가 여러 게시물 작성 (ON DELETE CASCADE)</t>
         </is>
       </c>
-      <c r="G17" s="78" t="n"/>
-      <c r="H17" s="78" t="n"/>
-      <c r="I17" s="78" t="n"/>
-      <c r="J17" s="79" t="n"/>
+      <c r="G17" s="84" t="n"/>
+      <c r="H17" s="84" t="n"/>
+      <c r="I17" s="84" t="n"/>
+      <c r="J17" s="85" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="80" t="inlineStr">
@@ -3072,6 +8003,8 @@
           <t>──────── 1 : N ────────▶</t>
         </is>
       </c>
+      <c r="C18" s="84" t="n"/>
+      <c r="D18" s="85" t="n"/>
       <c r="E18" s="82" t="inlineStr">
         <is>
           <t>sns_comments.user_id</t>
@@ -3082,10 +8015,10 @@
           <t>한 사용자가 여러 댓글 작성 (ON DELETE CASCADE)</t>
         </is>
       </c>
-      <c r="G18" s="78" t="n"/>
-      <c r="H18" s="78" t="n"/>
-      <c r="I18" s="78" t="n"/>
-      <c r="J18" s="79" t="n"/>
+      <c r="G18" s="84" t="n"/>
+      <c r="H18" s="84" t="n"/>
+      <c r="I18" s="84" t="n"/>
+      <c r="J18" s="85" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
@@ -3098,6 +8031,8 @@
           <t>──────── 1 : N ────────▶</t>
         </is>
       </c>
+      <c r="C19" s="84" t="n"/>
+      <c r="D19" s="85" t="n"/>
       <c r="E19" s="76" t="inlineStr">
         <is>
           <t>sns_comments.post_id</t>
@@ -3108,10 +8043,10 @@
           <t>한 게시물에 여러 댓글 (ON DELETE CASCADE)</t>
         </is>
       </c>
-      <c r="G19" s="78" t="n"/>
-      <c r="H19" s="78" t="n"/>
-      <c r="I19" s="78" t="n"/>
-      <c r="J19" s="79" t="n"/>
+      <c r="G19" s="84" t="n"/>
+      <c r="H19" s="84" t="n"/>
+      <c r="I19" s="84" t="n"/>
+      <c r="J19" s="85" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -3129,4 +8064,1592 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="86" t="inlineStr">
+        <is>
+          <t>👥  테이블: sns_follows   —   팔로우 관계</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>팔로우 / 팔로워 관계 저장 | 1차 필수 기능: 팔로우 시스템</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="88" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="88" t="inlineStr">
+        <is>
+          <t>컬럼명 (Column)</t>
+        </is>
+      </c>
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>데이터 타입</t>
+        </is>
+      </c>
+      <c r="D3" s="88" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="E3" s="88" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="F3" s="88" t="inlineStr">
+        <is>
+          <t>키 유형</t>
+        </is>
+      </c>
+      <c r="G3" s="88" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="H3" s="88" t="inlineStr">
+        <is>
+          <t>사용 화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="89" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B4" s="89" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D4" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E4" s="90" t="inlineStr">
+        <is>
+          <t>AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="F4" s="89" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G4" s="90" t="inlineStr">
+        <is>
+          <t>팔로우 관계 고유 번호</t>
+        </is>
+      </c>
+      <c r="H4" s="90" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B5" s="91" t="inlineStr">
+        <is>
+          <t>follower_id</t>
+        </is>
+      </c>
+      <c r="C5" s="92" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D5" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E5" s="92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="91" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G5" s="92" t="inlineStr">
+        <is>
+          <t>팔로우 하는 사람 — sns_users.id 참조</t>
+        </is>
+      </c>
+      <c r="H5" s="92" t="inlineStr">
+        <is>
+          <t>프로필, 팔로우</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="89" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>following_id</t>
+        </is>
+      </c>
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D6" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E6" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="89" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G6" s="90" t="inlineStr">
+        <is>
+          <t>팔로우 받는 사람 — sns_users.id 참조</t>
+        </is>
+      </c>
+      <c r="H6" s="90" t="inlineStr">
+        <is>
+          <t>프로필, 팔로우</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="91" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C7" s="92" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D7" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E7" s="92" t="inlineStr">
+        <is>
+          <t>NOW()</t>
+        </is>
+      </c>
+      <c r="F7" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="92" t="inlineStr">
+        <is>
+          <t>팔로우 시작 일시</t>
+        </is>
+      </c>
+      <c r="H7" s="92" t="inlineStr">
+        <is>
+          <t>마이페이지</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="93" t="inlineStr">
+        <is>
+          <t>🛠️  CREATE TABLE SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="94" t="inlineStr">
+        <is>
+          <t>CREATE TABLE sns_follows (</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    id           INT       NOT NULL AUTO_INCREMENT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    follower_id  INT       NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    following_id INT       NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    created_at   DATETIME  NOT NULL DEFAULT NOW(),</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PRIMARY KEY (id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    UNIQUE KEY uq_follow (follower_id, following_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_follower  (follower_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_following (following_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (follower_id)  REFERENCES sns_users(id) ON DELETE CASCADE,</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (following_id) REFERENCES sns_users(id) ON DELETE CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="94" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="86" t="inlineStr">
+        <is>
+          <t>📖  테이블: sns_stories   —   24시간 소멸 스토리</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>24시간 후 자동 소멸 스토리 저장 | 1차 필수 기능: 피드 &amp; 스토리</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="88" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="88" t="inlineStr">
+        <is>
+          <t>컬럼명 (Column)</t>
+        </is>
+      </c>
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>데이터 타입</t>
+        </is>
+      </c>
+      <c r="D3" s="88" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="E3" s="88" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="F3" s="88" t="inlineStr">
+        <is>
+          <t>키 유형</t>
+        </is>
+      </c>
+      <c r="G3" s="88" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="H3" s="88" t="inlineStr">
+        <is>
+          <t>사용 화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="89" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B4" s="89" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D4" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E4" s="90" t="inlineStr">
+        <is>
+          <t>AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="F4" s="89" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G4" s="90" t="inlineStr">
+        <is>
+          <t>스토리 고유 번호</t>
+        </is>
+      </c>
+      <c r="H4" s="90" t="inlineStr">
+        <is>
+          <t>홈 상단 스토리</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B5" s="91" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C5" s="92" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D5" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E5" s="92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="91" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G5" s="92" t="inlineStr">
+        <is>
+          <t>작성자 — sns_users.id 참조</t>
+        </is>
+      </c>
+      <c r="H5" s="92" t="inlineStr">
+        <is>
+          <t>홈 상단 스토리</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="89" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>image_url</t>
+        </is>
+      </c>
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>VARCHAR(500)</t>
+        </is>
+      </c>
+      <c r="D6" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E6" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="90" t="inlineStr">
+        <is>
+          <t>스토리 이미지 URL (Unsplash API)</t>
+        </is>
+      </c>
+      <c r="H6" s="90" t="inlineStr">
+        <is>
+          <t>홈 상단 스토리</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="91" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>caption</t>
+        </is>
+      </c>
+      <c r="C7" s="92" t="inlineStr">
+        <is>
+          <t>VARCHAR(300)</t>
+        </is>
+      </c>
+      <c r="D7" s="92" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E7" s="92" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F7" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="92" t="inlineStr">
+        <is>
+          <t>스토리 텍스트 (선택 입력)</t>
+        </is>
+      </c>
+      <c r="H7" s="92" t="inlineStr">
+        <is>
+          <t>홈 상단 스토리</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="89" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B8" s="89" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C8" s="90" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D8" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E8" s="90" t="inlineStr">
+        <is>
+          <t>NOW()</t>
+        </is>
+      </c>
+      <c r="F8" s="89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="90" t="inlineStr">
+        <is>
+          <t>스토리 작성 일시</t>
+        </is>
+      </c>
+      <c r="H8" s="90" t="inlineStr">
+        <is>
+          <t>홈 상단 스토리</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="91" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B9" s="91" t="inlineStr">
+        <is>
+          <t>expires_at</t>
+        </is>
+      </c>
+      <c r="C9" s="92" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D9" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E9" s="92" t="inlineStr">
+        <is>
+          <t>NOW()+24h</t>
+        </is>
+      </c>
+      <c r="F9" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="92" t="inlineStr">
+        <is>
+          <t>스토리 만료 일시 (created_at + 24시간)</t>
+        </is>
+      </c>
+      <c r="H9" s="92" t="inlineStr">
+        <is>
+          <t>홈 상단 스토리</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="93" t="inlineStr">
+        <is>
+          <t>🛠️  CREATE TABLE SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="94" t="inlineStr">
+        <is>
+          <t>CREATE TABLE sns_stories (</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    id         INT           NOT NULL AUTO_INCREMENT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    user_id    INT           NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    image_url  VARCHAR(500)  NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    caption    VARCHAR(300)  NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    created_at DATETIME      NOT NULL DEFAULT NOW(),</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    expires_at DATETIME      NOT NULL DEFAULT (NOW() + INTERVAL 24 HOUR),</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PRIMARY KEY (id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_user_id    (user_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_expires_at (expires_at),</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (user_id) REFERENCES sns_users(id) ON DELETE CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="94" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="95" t="inlineStr">
+        <is>
+          <t>-- 만료 스토리 자동 삭제 이벤트 (선택 적용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="95" t="inlineStr">
+        <is>
+          <t>-- CREATE EVENT evt_del_expired ON SCHEDULE EVERY 1 HOUR DO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="95" t="inlineStr">
+        <is>
+          <t>--   DELETE FROM sns_stories WHERE expires_at &lt; NOW();</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="86" t="inlineStr">
+        <is>
+          <t>👁  테이블: sns_story_views   —   스토리 조회 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>스토리 조회자 기록 (중복 방지, 조회수 집계) | 1차 필수 기능: 스토리</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="88" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="88" t="inlineStr">
+        <is>
+          <t>컬럼명 (Column)</t>
+        </is>
+      </c>
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>데이터 타입</t>
+        </is>
+      </c>
+      <c r="D3" s="88" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="E3" s="88" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="F3" s="88" t="inlineStr">
+        <is>
+          <t>키 유형</t>
+        </is>
+      </c>
+      <c r="G3" s="88" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="H3" s="88" t="inlineStr">
+        <is>
+          <t>사용 화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="89" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B4" s="89" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D4" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E4" s="90" t="inlineStr">
+        <is>
+          <t>AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="F4" s="89" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G4" s="90" t="inlineStr">
+        <is>
+          <t>조회 기록 고유 번호</t>
+        </is>
+      </c>
+      <c r="H4" s="90" t="inlineStr">
+        <is>
+          <t>스토리 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B5" s="91" t="inlineStr">
+        <is>
+          <t>story_id</t>
+        </is>
+      </c>
+      <c r="C5" s="92" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D5" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E5" s="92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="91" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G5" s="92" t="inlineStr">
+        <is>
+          <t>조회된 스토리 — sns_stories.id 참조</t>
+        </is>
+      </c>
+      <c r="H5" s="92" t="inlineStr">
+        <is>
+          <t>스토리 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="89" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>viewer_id</t>
+        </is>
+      </c>
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D6" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E6" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="89" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G6" s="90" t="inlineStr">
+        <is>
+          <t>조회한 사용자 — sns_users.id 참조</t>
+        </is>
+      </c>
+      <c r="H6" s="90" t="inlineStr">
+        <is>
+          <t>스토리 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="91" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>viewed_at</t>
+        </is>
+      </c>
+      <c r="C7" s="92" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D7" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E7" s="92" t="inlineStr">
+        <is>
+          <t>NOW()</t>
+        </is>
+      </c>
+      <c r="F7" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="92" t="inlineStr">
+        <is>
+          <t>조회 일시</t>
+        </is>
+      </c>
+      <c r="H7" s="92" t="inlineStr">
+        <is>
+          <t>스토리 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="93" t="inlineStr">
+        <is>
+          <t>🛠️  CREATE TABLE SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="94" t="inlineStr">
+        <is>
+          <t>CREATE TABLE sns_story_views (</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    id        INT       NOT NULL AUTO_INCREMENT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    story_id  INT       NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    viewer_id INT       NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    viewed_at DATETIME  NOT NULL DEFAULT NOW(),</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PRIMARY KEY (id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    UNIQUE KEY uq_story_view (story_id, viewer_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_story_id  (story_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_viewer_id (viewer_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (story_id)  REFERENCES sns_stories(id) ON DELETE CASCADE,</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (viewer_id) REFERENCES sns_users(id)   ON DELETE CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="94" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="86" t="inlineStr">
+        <is>
+          <t>❤  테이블: sns_likes   —   게시물 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>사용자별 좋아요 기록 (중복 방지 + 취소 가능) | 1차 필수 기능: 좋아요 &amp; 댓글</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="88" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="88" t="inlineStr">
+        <is>
+          <t>컬럼명 (Column)</t>
+        </is>
+      </c>
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>데이터 타입</t>
+        </is>
+      </c>
+      <c r="D3" s="88" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="E3" s="88" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="F3" s="88" t="inlineStr">
+        <is>
+          <t>키 유형</t>
+        </is>
+      </c>
+      <c r="G3" s="88" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="H3" s="88" t="inlineStr">
+        <is>
+          <t>사용 화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="89" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B4" s="89" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D4" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E4" s="90" t="inlineStr">
+        <is>
+          <t>AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="F4" s="89" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G4" s="90" t="inlineStr">
+        <is>
+          <t>좋아요 기록 고유 번호</t>
+        </is>
+      </c>
+      <c r="H4" s="90" t="inlineStr">
+        <is>
+          <t>피드, 게시물 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B5" s="91" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C5" s="92" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D5" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E5" s="92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="91" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G5" s="92" t="inlineStr">
+        <is>
+          <t>좋아요 누른 사용자 — sns_users.id 참조</t>
+        </is>
+      </c>
+      <c r="H5" s="92" t="inlineStr">
+        <is>
+          <t>피드, 게시물 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="89" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>post_id</t>
+        </is>
+      </c>
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D6" s="90" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E6" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="89" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G6" s="90" t="inlineStr">
+        <is>
+          <t>좋아요 대상 게시물 — sns_posts.id 참조</t>
+        </is>
+      </c>
+      <c r="H6" s="90" t="inlineStr">
+        <is>
+          <t>피드, 게시물 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="91" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C7" s="92" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D7" s="92" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E7" s="92" t="inlineStr">
+        <is>
+          <t>NOW()</t>
+        </is>
+      </c>
+      <c r="F7" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="92" t="inlineStr">
+        <is>
+          <t>좋아요 누른 일시</t>
+        </is>
+      </c>
+      <c r="H7" s="92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="96" t="inlineStr">
+        <is>
+          <t>📌 설계 주의사항: sns_posts.likes_count는 캐시 값으로 유지 — 아래 트리거로 INSERT/DELETE 시 자동 갱신 권장</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="93" t="inlineStr">
+        <is>
+          <t>🛠️  CREATE TABLE SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="94" t="inlineStr">
+        <is>
+          <t>CREATE TABLE sns_likes (</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    id         INT       NOT NULL AUTO_INCREMENT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    user_id    INT       NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    post_id    INT       NOT NULL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    created_at DATETIME  NOT NULL DEFAULT NOW(),</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PRIMARY KEY (id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    UNIQUE KEY uq_like (user_id, post_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_post_id (post_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDEX idx_user_id (user_id),</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (user_id) REFERENCES sns_users(id) ON DELETE CASCADE,</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (post_id) REFERENCES sns_posts(id) ON DELETE CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="94" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="95" t="inlineStr">
+        <is>
+          <t>-- 좋아요 추가 시 likes_count 자동 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="94" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER trg_like_insert AFTER INSERT ON sns_likes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FOR EACH ROW UPDATE sns_posts SET likes_count = likes_count + 1 WHERE id = NEW.post_id;</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="95" t="inlineStr">
+        <is>
+          <t>-- 좋아요 취소 시 likes_count 자동 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="94" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER trg_like_delete AFTER DELETE ON sns_likes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FOR EACH ROW UPDATE sns_posts SET likes_count = likes_count - 1 WHERE id = OLD.post_id;</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A19:H19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>